--- a/PSP_providers_glossary_builder/data/input/PSP_providers_labeled.xlsx
+++ b/PSP_providers_glossary_builder/data/input/PSP_providers_labeled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\glossary-builder-local-v7\PSP_providers_glossary_builder\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4F1EA1-7A5D-4DFB-8DFD-AC438A440B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0749027D-72AD-4C94-94DE-13D8BF78D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Примеры" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="247">
   <si>
     <t>text</t>
   </si>
@@ -2240,6 +2240,292 @@
   </si>
   <si>
     <t>null by rows</t>
+  </si>
+  <si>
+    <t>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+ 📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍️Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍️Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная ссылка➖
+🔴1000 - 100.000 ➡️ 12%
+🔴100 - 999 ➡️ 15%
+👻 БТ ➖
+🔴1.000₽ - 5.000₽ ➡️ **16%**
+📃 Курс Rapira
+🎅Монобанки➖
+✍️🏦➡️🏦 Сбер-Сбер:
+🔴от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+✍️🇷🇺➡️🇷🇺 ВТБ - ВТБ:
+🔴 от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+🌐Альтернативные ГЕО➖
+✍️🇦🇿Азербайджан:
+🔴Вход ➡️  **4%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+✍️🇰🇿Казахстан:
+🔴Вход ➡️ **4.5%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+🔗Страховые депозиты➖
+▶️БТ - 500$
+▶️РФ - 600$
+▶️Моб ком - 250$
+▶️AZN - 600$
+▶️KZ - 600$
+💬За подключением в лс юз: rezhunozhem</t>
+  </si>
+  <si>
+    <t>🐫 CameL  подключит на TradeMO 🤩
+🤩 Общий трафик СБП + карты с уже готовыми решениями под залив и «ферму»:
+💰 0₽–1999₽ — 13%
+💰 2001₽–4000₽ — 7,5%
+💰 от 4000₽ — 7%
+💰 от 10.000₽ — 6%
+🔄 В круг: до 16,5% 🤩
+🔥 VIP SBP (только проверенные КА + высокий чек):
+💰 2001₽–4000₽ — 7,5%
+💰 от 4000₽ — 7%
+🔄 В круг: до 10,5% 🤩
+🏦 Альфа → Альфа (с подробными инструкциями):
+💸 Любая сумма — 6,5%
+🔄 В круг: до 9,5% 🤩
+📱 SIM-направление (мануал + бот откупа):
+💰 до 2000₽ — 13%
+🔄 В круг: до 16% 🤩
+📊 Единая сетка выплат по всем направлениям:
+▫️ до 15.000₽ — 3%
+▫️ 15.000₽–35.000₽ — 2%
+▫️ 35.000₽–70.000₽ — 2,5%
+▫️ 70.000₽–300.000₽ — 2%
+⏰ Prime Time бонус: +0,5–1% к профиту 🤩
+💱 Единый курс RUB:
+🤩 Рапира +1%
+🤩Первая строка
+🤩 Красный стакан
+🤩 Запуск ваших методов с полной поддержкой и сопровождением
+🤩 Уникальный маркетплейс мануалов «ТМетод»
+🐫 За подробностями — в ЛС  @cameltll 🐫</t>
+  </si>
+  <si>
+    <t>**🔥**** ПОДКЛЮЧИТЬСЯ К GO6 ****🔥****
+****🌐****Ставки:
+****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****
+****➡️****16% чеки 100–999****🪙****
+****➡️****14% чеки 1 000–4 999****🪙****
+****➡️****12% чеки от 5 000****🪙****
+****➡️****8% на VIP чеки от 10 000****🪙****
+****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****
+****😨****Выплаты - 2****🤍****
+****🛜**** Своим трейдерам предоставляю мануалы на моб ком, гу, физ карты
+****📣****Для связи - **
+**rezhunozhem
+Young_Knife
+Butterflly_Knife**</t>
+  </si>
+  <si>
+    <t>🤩 **Pay4Amg** 🤩
+📢**Pay in**(Сбп/С2С):
+🟠**1-5к - 13.5%**
+🟠**5-10к - 12.5%**
+🟠**10к+ - 10%**
+📢**Pay out**(Сбп/С2С):
+🟠**1% за все чеки** (Rapira)
+🟠**Трангсран огромные объемы**
+🟠**Моб коммерция - 16%**
+🟠**Любые монобанки**
+🟠**НСПК** (как мультик, так и ру)
+🟠**Качественные контрагенты**
+🟠**БТ с PDF чеками - 9.5%**
+📢**Новые гео** в работе:
+🇹🇯**Таджикистан**
+🇰🇿**Казахстан**
+🇻🇪**Венесуэла**
+🇺🇿**Узбекистан**
+🇦🇷**Аргентина**
+🇮🇳**Индия**
+🇪🇬**Египет**
+🇦🇿**Азербайджан**
+❕**По остальным гео уточнять, сможем добавить по запросу**
+⚡️**Огромные объемы** трафика, классный интерфейс, **поддержка 24/7** для каждого трейдера!
+✔️**Частые розыгрыши**, созвоны, личные менторы и **штатные тимлиды**, которые помогут вам работать с любым материалом и выжимать из него **максимум**
+❕Для тимлидов **пожизненный 1%** за приведенных трейдеров + **бонусы от меня**
+⚡️**KYC ДЛЯ РАБОТЫ НЕ НУЖЕН**
+**Работай с лучшими** - 🤩
+✈️**По поводу подключения** - @pay4amg_ceo</t>
+  </si>
+  <si>
+    <t>B-1</t>
+  </si>
+  <si>
+    <t>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+ 📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍️Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍️Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная ссылка➖
+🔴1000 - 100.000 ➡️ 12%
+🔴100 - 999 ➡️ 15%
+👻 БТ ➖
+🔴1.000₽ - 5.000₽ ➡️ **16%**
+📃 Курс Rapira
+🎅Монобанки➖
+✍️🏦➡️🏦 Сбер-Сбер:
+🔴от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+✍️🇷🇺➡️🇷🇺 ВТБ - ВТБ:
+🔴 от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+🌐Альтернативные ГЕО➖
+✍️🇦🇿Азербайджан:
+🔴Вход ➡️  **4%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+✍️🇰🇿Казахстан:
+🔴Вход ➡️ **4.5%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+🔗Страховые депозиты➖
+▶️БТ - 500$
+▶️РФ - 600$
+▶️Моб ком - 250$
+▶️AZN - 600$
+▶️KZ - 600$
+💬За подключением в лс</t>
+  </si>
+  <si>
+    <t>**GIRA &amp; PAY2PROFIT обновляют СТАВКИ**
+❗️Специально для своих выбила лучшие условия подключения👇
+**Классика, фермы, залив:**
+0-99к/сутки - 10.5%
+100к-199к/сутки - 11.5%
+от 200к/сутки - 12.5%
+❗️Высокие обороты - индивидуальная ставка
+**БТ:**
+12.5%
+❗️Стабильный оборот от 100к/сутки - повышенная ставка
+**МК:**
+15%
+Страховой депозит прогрессивный - 10% от суточного оборота
+**Минимальный страховой - 150$**
+Пиши сейчас - работай уже через 60 минут
+💌За подключением: @Gira_TL</t>
+  </si>
+  <si>
+    <t>🚨 **Pro-Level Platform + CRM Built to Crush the Market** 🚨
+⚡️ Flawless 24/7 performance &amp; full automation
+📈 Perfect for Forex, Crypto, CFD &amp; Recovery brands
+💳 Seamless PSP integration – more deposits, less hassle
+🌟 **Your own branded website FREE with every deal**
+🔥 Stop settling for average, level up NOW
+💥 **Everything you need is waiting in my bio**</t>
+  </si>
+  <si>
+    <t>☑️ **Подключение к Cube** 🙈
+🔮**C2C / СБП**
+🔴от 1к до 5к ➡️ 15% 
+🔴до 10к ➡️ 13% 
+🦋 **МЕЛКОЧЕК**
+🔴 до 1к ➡️ 17%
+☠️ **КОНТР-АГЕНТЫ** ➡️ 10%
+📝**QR НСПК**
+🔴до 5к ➡️ 16%
+🔴от 5к ➡️ 13%
+✍️огромные объемы трафика✍️
+🛒 **ЯНДЕКС ЧАЕВЫЕ** ➡️ 13%
+✈️ **МОБКОМ**
+🔴до 1к ➡️ 15%
+🔴от 1к ➡️ 15%
+🔴Выход ➡️ 2% 
+📃(Рапира, средн.по стакану) 
+👻БТ out ➡️ 2% 
+🪭OCT out  ➡️ 1%
+🌐 **ТРАНСГРАН** ➡️ 7%
+👑**Локальный трафик****➖**
+🇦🇿 Азербайджан ➡️ 5/1,5%
+🇦🇷 Аргентина ➡️ 4/1%
+🇧🇷 Бразилия ➡️ 0,5/0,5%
+🇪🇬 Египет ➡️ 5/2%
+🇰🇿 Казахстан ➡️ 7/2%
+🇰🇬 Кыргызстан ➡️ 4/1%
+🇲🇩 Молдова ➡️ 5/1,5%
+🇰🇷Южная Корея ➡️ 6/1%
+🇹🇷 Турция ➡️ 5/1,5%
+🇺🇿 Узбекистан ➡️ 1.5/2
+🕷️Страховой депозит: 500$
+🔗Апелляционный депозит: 500$
+💬За подключением в лс - ☑️ **Подключение к Cube** 🙈
+🔮**C2C / СБП**
+🔴от 1к до 5к ➡️ 15% 
+🔴до 10к ➡️ 13% 
+🦋 **МЕЛКОЧЕК**
+🔴 до 1к ➡️ 17%
+☠️ **КОНТР-АГЕНТЫ** ➡️ 10%
+📝**QR НСПК**
+🔴до 5к ➡️ 16%
+🔴от 5к ➡️ 13%
+✍️огромные объемы трафика✍️
+🛒 **ЯНДЕКС ЧАЕВЫЕ** ➡️ 13%
+✈️ **МОБКОМ**
+🔴до 1к ➡️ 15%
+🔴от 1к ➡️ 15%
+🔴Выход ➡️ 2% 
+📃(Рапира, средн.по стакану) 
+👻БТ out ➡️ 2% 
+🪭OCT out  ➡️ 1%
+🌐 **ТРАНСГРАН** ➡️ 7%
+👑**Локальный трафик****➖**
+🇦🇿 Азербайджан ➡️ 5/1,5%
+🇦🇷 Аргентина ➡️ 4/1%
+🇧🇷 Бразилия ➡️ 0,5/0,5%
+🇪🇬 Египет ➡️ 5/2%
+🇰🇿 Казахстан ➡️ 7/2%
+🇰🇬 Кыргызстан ➡️ 4/1%
+🇲🇩 Молдова ➡️ 5/1,5%
+🇰🇷Южная Корея ➡️ 6/1%
+🇹🇷 Турция ➡️ 5/1,5%
+🇺🇿 Узбекистан ➡️ 1.5/2
+🕷️Страховой депозит: 500$
+🔗Апелляционный депозит: 500$
+💬За подключением в лс - rezhunozhem  Butterflly_Knife</t>
   </si>
 </sst>
 </file>
@@ -2594,19 +2880,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7B8F7DB-D023-4846-A9F9-92FF6D427265}" name="Таблиця1" displayName="Таблиця1" ref="A1:D224" totalsRowShown="0">
-  <autoFilter ref="A1:D224" xr:uid="{D7B8F7DB-D023-4846-A9F9-92FF6D427265}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="A1"/>
-        <filter val="A2"/>
-        <filter val="B1"/>
-        <filter val="B2"/>
-        <filter val="B3"/>
-        <filter val="B4"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7B8F7DB-D023-4846-A9F9-92FF6D427265}" name="Таблиця1" displayName="Таблиця1" ref="A1:D234" totalsRowShown="0">
+  <autoFilter ref="A1:D234" xr:uid="{D7B8F7DB-D023-4846-A9F9-92FF6D427265}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{FF98355E-C806-44FE-89E8-A8F3B48556C4}" name="text"/>
     <tableColumn id="2" xr3:uid="{568E87A1-2334-45E4-8360-46552F0810D1}" name="group"/>
@@ -2880,7 +3155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.6640625" customWidth="1"/>
@@ -4609,7 +4884,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>122</v>
       </c>
@@ -4623,7 +4898,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="19" t="s">
         <v>140</v>
       </c>
@@ -4637,7 +4912,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="20" t="s">
         <v>141</v>
       </c>
@@ -4651,7 +4926,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="20" t="s">
         <v>142</v>
       </c>
@@ -4665,7 +4940,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="245.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="20" t="s">
         <v>143</v>
       </c>
@@ -4679,7 +4954,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="173.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="20" t="s">
         <v>144</v>
       </c>
@@ -4693,7 +4968,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="288.60000000000002" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="19" t="s">
         <v>145</v>
       </c>
@@ -4707,7 +4982,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="173.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="19" t="s">
         <v>146</v>
       </c>
@@ -4721,7 +4996,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="144.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="19" t="s">
         <v>147</v>
       </c>
@@ -4735,7 +5010,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="202.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="20" t="s">
         <v>148</v>
       </c>
@@ -4749,7 +5024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="20" t="s">
         <v>149</v>
       </c>
@@ -4763,7 +5038,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="115.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="19" t="s">
         <v>150</v>
       </c>
@@ -4777,7 +5052,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="115.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="19" t="s">
         <v>151</v>
       </c>
@@ -4791,7 +5066,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="20" t="s">
         <v>152</v>
       </c>
@@ -4805,7 +5080,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="144.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="19" t="s">
         <v>153</v>
       </c>
@@ -4819,7 +5094,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="288.60000000000002" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="19" t="s">
         <v>154</v>
       </c>
@@ -4833,7 +5108,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="115.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="20" t="s">
         <v>155</v>
       </c>
@@ -4847,7 +5122,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="331.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" ht="331.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="20" t="s">
         <v>156</v>
       </c>
@@ -4861,7 +5136,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="130.19999999999999" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="19" t="s">
         <v>157</v>
       </c>
@@ -4875,7 +5150,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="20" t="s">
         <v>158</v>
       </c>
@@ -4889,7 +5164,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="288.60000000000002" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="19" t="s">
         <v>154</v>
       </c>
@@ -4903,7 +5178,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="19" t="s">
         <v>159</v>
       </c>
@@ -4917,7 +5192,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="20" t="s">
         <v>160</v>
       </c>
@@ -4931,7 +5206,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="20" t="s">
         <v>161</v>
       </c>
@@ -4945,7 +5220,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="87" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="20" t="s">
         <v>162</v>
       </c>
@@ -4959,7 +5234,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="173.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="20" t="s">
         <v>163</v>
       </c>
@@ -4973,7 +5248,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="87" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="20" t="s">
         <v>164</v>
       </c>
@@ -4987,7 +5262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="115.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="19" t="s">
         <v>165</v>
       </c>
@@ -5001,7 +5276,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="144.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="19" t="s">
         <v>166</v>
       </c>
@@ -5015,7 +5290,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="20" t="s">
         <v>167</v>
       </c>
@@ -5029,7 +5304,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="19" t="s">
         <v>168</v>
       </c>
@@ -5043,7 +5318,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="259.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" ht="259.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="20" t="s">
         <v>169</v>
       </c>
@@ -5057,7 +5332,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="20" t="s">
         <v>23</v>
       </c>
@@ -5071,7 +5346,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="72.599999999999994" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="19" t="s">
         <v>170</v>
       </c>
@@ -5085,7 +5360,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="19" t="s">
         <v>171</v>
       </c>
@@ -5099,7 +5374,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="20" t="s">
         <v>172</v>
       </c>
@@ -5113,7 +5388,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="130.19999999999999" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="19" t="s">
         <v>157</v>
       </c>
@@ -5127,7 +5402,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="19" t="s">
         <v>173</v>
       </c>
@@ -5141,7 +5416,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="20" t="s">
         <v>174</v>
       </c>
@@ -5155,7 +5430,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="130.19999999999999" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="19" t="s">
         <v>175</v>
       </c>
@@ -5169,7 +5444,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="19" t="s">
         <v>176</v>
       </c>
@@ -5183,7 +5458,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="245.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="20" t="s">
         <v>177</v>
       </c>
@@ -5197,7 +5472,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="259.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" ht="259.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="19" t="s">
         <v>178</v>
       </c>
@@ -5211,7 +5486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="19" t="s">
         <v>179</v>
       </c>
@@ -5225,7 +5500,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="19" t="s">
         <v>180</v>
       </c>
@@ -5239,7 +5514,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="29.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="19" t="s">
         <v>181</v>
       </c>
@@ -5253,7 +5528,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="130.19999999999999" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="20" t="s">
         <v>182</v>
       </c>
@@ -5267,7 +5542,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="187.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="20" t="s">
         <v>183</v>
       </c>
@@ -5281,7 +5556,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="29.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="19" t="s">
         <v>184</v>
       </c>
@@ -5295,7 +5570,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="19" t="s">
         <v>185</v>
       </c>
@@ -5309,7 +5584,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="101.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="20" t="s">
         <v>186</v>
       </c>
@@ -5323,7 +5598,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="202.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="20" t="s">
         <v>187</v>
       </c>
@@ -5337,7 +5612,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="19" t="s">
         <v>188</v>
       </c>
@@ -5351,7 +5626,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="20" t="s">
         <v>189</v>
       </c>
@@ -5365,7 +5640,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="20" t="s">
         <v>190</v>
       </c>
@@ -5379,7 +5654,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="144.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="19" t="s">
         <v>191</v>
       </c>
@@ -5393,7 +5668,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="115.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="20" t="s">
         <v>192</v>
       </c>
@@ -5407,7 +5682,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="21" t="s">
         <v>195</v>
       </c>
@@ -5421,7 +5696,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="87" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="22" t="s">
         <v>196</v>
       </c>
@@ -5435,7 +5710,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="187.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="23" t="s">
         <v>197</v>
       </c>
@@ -5449,7 +5724,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="389.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="389.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="22" t="s">
         <v>198</v>
       </c>
@@ -5463,7 +5738,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="23" t="s">
         <v>199</v>
       </c>
@@ -5477,7 +5752,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="22" t="s">
         <v>200</v>
       </c>
@@ -5491,7 +5766,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="24" t="s">
         <v>201</v>
       </c>
@@ -5505,7 +5780,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="245.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="21" t="s">
         <v>202</v>
       </c>
@@ -5519,7 +5794,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="22" t="s">
         <v>203</v>
       </c>
@@ -5533,7 +5808,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="101.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="23" t="s">
         <v>204</v>
       </c>
@@ -5547,7 +5822,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="245.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="22" t="s">
         <v>205</v>
       </c>
@@ -5561,7 +5836,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="159" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" ht="159" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="23" t="s">
         <v>206</v>
       </c>
@@ -5575,7 +5850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="22" t="s">
         <v>207</v>
       </c>
@@ -5589,7 +5864,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="23" t="s">
         <v>208</v>
       </c>
@@ -5603,7 +5878,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="22" t="s">
         <v>209</v>
       </c>
@@ -5617,7 +5892,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="23" t="s">
         <v>210</v>
       </c>
@@ -5631,7 +5906,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="187.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="22" t="s">
         <v>211</v>
       </c>
@@ -5645,7 +5920,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="23" t="s">
         <v>212</v>
       </c>
@@ -5659,7 +5934,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="130.19999999999999" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="22" t="s">
         <v>213</v>
       </c>
@@ -5673,7 +5948,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="317.39999999999998" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" ht="317.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="23" t="s">
         <v>214</v>
       </c>
@@ -5687,7 +5962,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="72.599999999999994" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="22" t="s">
         <v>215</v>
       </c>
@@ -5701,7 +5976,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="23" t="s">
         <v>216</v>
       </c>
@@ -5715,7 +5990,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="58.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="22" t="s">
         <v>25</v>
       </c>
@@ -5729,7 +6004,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="23" t="s">
         <v>217</v>
       </c>
@@ -5743,7 +6018,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="22" t="s">
         <v>218</v>
       </c>
@@ -5757,7 +6032,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="231" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="23" t="s">
         <v>219</v>
       </c>
@@ -5771,7 +6046,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="22" t="s">
         <v>220</v>
       </c>
@@ -5785,7 +6060,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="23" t="s">
         <v>221</v>
       </c>
@@ -5799,7 +6074,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="22" t="s">
         <v>222</v>
       </c>
@@ -5813,7 +6088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="288.60000000000002" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="23" t="s">
         <v>223</v>
       </c>
@@ -5827,7 +6102,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="87" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="22" t="s">
         <v>9</v>
       </c>
@@ -5841,7 +6116,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="187.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="23" t="s">
         <v>224</v>
       </c>
@@ -5855,7 +6130,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="303" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" ht="303" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="22" t="s">
         <v>225</v>
       </c>
@@ -5869,7 +6144,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="274.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="23" t="s">
         <v>226</v>
       </c>
@@ -5883,7 +6158,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="274.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="22" t="s">
         <v>227</v>
       </c>
@@ -5897,7 +6172,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="274.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="23" t="s">
         <v>228</v>
       </c>
@@ -5911,7 +6186,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="22" t="s">
         <v>229</v>
       </c>
@@ -5925,7 +6200,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="23" t="s">
         <v>230</v>
       </c>
@@ -5939,7 +6214,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="72.599999999999994" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="22" t="s">
         <v>231</v>
       </c>
@@ -5953,7 +6228,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="23" t="s">
         <v>232</v>
       </c>
@@ -5967,7 +6242,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="144.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="22" t="s">
         <v>233</v>
       </c>
@@ -5981,7 +6256,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="23" t="s">
         <v>234</v>
       </c>
@@ -5995,7 +6270,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="409.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="22" t="s">
         <v>235</v>
       </c>
@@ -6009,7 +6284,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A224" s="24" t="s">
         <v>236</v>
       </c>
@@ -6021,6 +6296,146 @@
       </c>
       <c r="D224" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B225" t="s">
+        <v>242</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B226" t="s">
+        <v>242</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B227" t="s">
+        <v>242</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B228" t="s">
+        <v>242</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B229" t="s">
+        <v>242</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B230" t="s">
+        <v>242</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A231" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B231" t="s">
+        <v>242</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A232" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B232" t="s">
+        <v>242</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A233" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B233" t="s">
+        <v>242</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A234" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B234" t="s">
+        <v>242</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -6240,6 +6655,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8">
+        <f>COUNTIFS(Таблиця1[text], "&lt;&gt;", Таблиця1[group], A8)</f>
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <f>COUNTIF(Таблиця1[group],Саммари!A8)</f>
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8" si="1">C8-B8</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>COUNTIFS(Таблиця1[text], "&lt;&gt;", Таблиця1[group], A8, Таблиця1[lang], "ru")</f>
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <f>COUNTIFS(Таблиця1[text], "&lt;&gt;", Таблиця1[group], A8, Таблиця1[lang], "en")</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>193</v>
@@ -6280,11 +6720,11 @@
       </c>
       <c r="B13">
         <f>SUM(B2:B12)</f>
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C13">
         <f>SUM(C2:C12)</f>
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D13">
         <f>SUM(D2:D12)</f>
@@ -6292,7 +6732,7 @@
       </c>
       <c r="E13">
         <f>SUM(E2:E12)</f>
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F13">
         <f>SUM(F2:F12)</f>
@@ -6307,7 +6747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECB21B5-48E1-40D6-B725-E3B4A7716B36}">
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -6315,7 +6755,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1:D123">_xlfn._xlws.FILTER(Таблиця1[], (Таблиця1[group]&lt;&gt;"A0") * (Таблиця1[group]&lt;&gt;"B0"))</f>
+        <f t="array" ref="A1:D133">_xlfn._xlws.FILTER(Таблиця1[], (Таблиця1[group]&lt;&gt;"A0") * (Таблиця1[group]&lt;&gt;"B0"))</f>
         <v>#Selling #Payment 
 Kunga — licensed PSP 
 89% approval rate | Any industry | Fast Onboarding | T+0
@@ -8581,6 +9021,443 @@
         <v>en</v>
       </c>
     </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" t="str">
+        <v>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+ 📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍️Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍️Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная ссылка➖
+🔴1000 - 100.000 ➡️ 12%
+🔴100 - 999 ➡️ 15%
+👻 БТ ➖
+🔴1.000₽ - 5.000₽ ➡️ **16%**
+📃 Курс Rapira
+🎅Монобанки➖
+✍️🏦➡️🏦 Сбер-Сбер:
+🔴от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+✍️🇷🇺➡️🇷🇺 ВТБ - ВТБ:
+🔴 от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+🌐Альтернативные ГЕО➖
+✍️🇦🇿Азербайджан:
+🔴Вход ➡️  **4%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+✍️🇰🇿Казахстан:
+🔴Вход ➡️ **4.5%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+🔗Страховые депозиты➖
+▶️БТ - 500$
+▶️РФ - 600$
+▶️Моб ком - 250$
+▶️AZN - 600$
+▶️KZ - 600$
+💬За подключением в лс юз: rezhunozhem</v>
+      </c>
+      <c r="B124" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" t="str">
+        <v>🐫 CameL  подключит на TradeMO 🤩
+🤩 Общий трафик СБП + карты с уже готовыми решениями под залив и «ферму»:
+💰 0₽–1999₽ — 13%
+💰 2001₽–4000₽ — 7,5%
+💰 от 4000₽ — 7%
+💰 от 10.000₽ — 6%
+🔄 В круг: до 16,5% 🤩
+🔥 VIP SBP (только проверенные КА + высокий чек):
+💰 2001₽–4000₽ — 7,5%
+💰 от 4000₽ — 7%
+🔄 В круг: до 10,5% 🤩
+🏦 Альфа → Альфа (с подробными инструкциями):
+💸 Любая сумма — 6,5%
+🔄 В круг: до 9,5% 🤩
+📱 SIM-направление (мануал + бот откупа):
+💰 до 2000₽ — 13%
+🔄 В круг: до 16% 🤩
+📊 Единая сетка выплат по всем направлениям:
+▫️ до 15.000₽ — 3%
+▫️ 15.000₽–35.000₽ — 2%
+▫️ 35.000₽–70.000₽ — 2,5%
+▫️ 70.000₽–300.000₽ — 2%
+⏰ Prime Time бонус: +0,5–1% к профиту 🤩
+💱 Единый курс RUB:
+🤩 Рапира +1%
+🤩Первая строка
+🤩 Красный стакан
+🤩 Запуск ваших методов с полной поддержкой и сопровождением
+🤩 Уникальный маркетплейс мануалов «ТМетод»
+🐫 За подробностями — в ЛС  @cameltll 🐫</v>
+      </c>
+      <c r="B125" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" t="str">
+        <v>**🔥**** ПОДКЛЮЧИТЬСЯ К GO6 ****🔥****
+****🌐****Ставки:
+****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****
+****➡️****16% чеки 100–999****🪙****
+****➡️****14% чеки 1 000–4 999****🪙****
+****➡️****12% чеки от 5 000****🪙****
+****➡️****8% на VIP чеки от 10 000****🪙****
+****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****
+****😨****Выплаты - 2****🤍****
+****🛜**** Своим трейдерам предоставляю мануалы на моб ком, гу, физ карты
+****📣****Для связи - **
+**rezhunozhem
+Young_Knife
+Butterflly_Knife**</v>
+      </c>
+      <c r="B126" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" t="str">
+        <v>❗️**DECRYPT ОБНОВЛЯЕТ СТАВКИ****❗️****
+**Трафик - чистый гембет**
+**
+✅Предоставляем подробные мануалы для качественной работы
+✅Помогаем быстро выйти на стабильный результат
+✅Помогаем на всех этапах
+🟡**МК**
+100**₽** - ∞ **→ 13.5%**
+🟡**СБП/С2С**
+**1.000₽ – 4.999₽ → 9.5%**
+**5.000₽ – 9.999₽ → 8.5%**
+**10.000₽ – 14.999₽ → 7.5%**
+**15.000₽ – 19.999₽ → 7%**
+**от 20.000₽ → 6.5%**
+🟡**ГУ**
+1.000**₽** - ∞ **→ 8.5%**
+🔒**Страховой депозит**
+• **100₽** - **10.000₽** — **500 $**
+• **От** **10.000₽** — **1000 $****
+За подключением: ****@Moryak_DecryptPay**</v>
+      </c>
+      <c r="B127" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" t="str">
+        <v>🤩 **Pay4Amg** 🤩
+📢**Pay in**(Сбп/С2С):
+🟠**1-5к - 13.5%**
+🟠**5-10к - 12.5%**
+🟠**10к+ - 10%**
+📢**Pay out**(Сбп/С2С):
+🟠**1% за все чеки** (Rapira)
+🟠**Трангсран огромные объемы**
+🟠**Моб коммерция - 16%**
+🟠**Любые монобанки**
+🟠**НСПК** (как мультик, так и ру)
+🟠**Качественные контрагенты**
+🟠**БТ с PDF чеками - 9.5%**
+📢**Новые гео** в работе:
+🇹🇯**Таджикистан**
+🇰🇿**Казахстан**
+🇻🇪**Венесуэла**
+🇺🇿**Узбекистан**
+🇦🇷**Аргентина**
+🇮🇳**Индия**
+🇪🇬**Египет**
+🇦🇿**Азербайджан**
+❕**По остальным гео уточнять, сможем добавить по запросу**
+⚡️**Огромные объемы** трафика, классный интерфейс, **поддержка 24/7** для каждого трейдера!
+✔️**Частые розыгрыши**, созвоны, личные менторы и **штатные тимлиды**, которые помогут вам работать с любым материалом и выжимать из него **максимум**
+❕Для тимлидов **пожизненный 1%** за приведенных трейдеров + **бонусы от меня**
+⚡️**KYC ДЛЯ РАБОТЫ НЕ НУЖЕН**
+**Работай с лучшими** - 🤩
+✈️**По поводу подключения** - @pay4amg_ceo</v>
+      </c>
+      <c r="B128" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" t="str">
+        <v>❗️**DECRYPT ОБНОВЛЯЕТ СТАВКИ****❗️****
+**Трафик - чистый гембет**
+**
+✅Предоставляем подробные мануалы для качественной работы
+✅Помогаем быстро выйти на стабильный результат
+✅Помогаем на всех этапах
+🟡**МК**
+100**₽** - ∞ **→ 13.5%**
+🟡**СБП/С2С**
+**1.000₽ – 4.999₽ → 9.5%**
+**5.000₽ – 9.999₽ → 8.5%**
+**10.000₽ – 14.999₽ → 7.5%**
+**15.000₽ – 19.999₽ → 7%**
+**от 20.000₽ → 6.5%**
+🟡**ГУ**
+1.000**₽** - ∞ **→ 8.5%**
+🔒**Страховой депозит**
+• **100₽** - **10.000₽** — **500 $**
+• **От** **10.000₽** — **1000 $****
+За подключением: ****@Moryak_DecryptPay**</v>
+      </c>
+      <c r="B129" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="str">
+        <v>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+ 📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍️Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍️Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная ссылка➖
+🔴1000 - 100.000 ➡️ 12%
+🔴100 - 999 ➡️ 15%
+👻 БТ ➖
+🔴1.000₽ - 5.000₽ ➡️ **16%**
+📃 Курс Rapira
+🎅Монобанки➖
+✍️🏦➡️🏦 Сбер-Сбер:
+🔴от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+✍️🇷🇺➡️🇷🇺 ВТБ - ВТБ:
+🔴 от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+🌐Альтернативные ГЕО➖
+✍️🇦🇿Азербайджан:
+🔴Вход ➡️  **4%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+✍️🇰🇿Казахстан:
+🔴Вход ➡️ **4.5%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+🔗Страховые депозиты➖
+▶️БТ - 500$
+▶️РФ - 600$
+▶️Моб ком - 250$
+▶️AZN - 600$
+▶️KZ - 600$
+💬За подключением в лс</v>
+      </c>
+      <c r="B130" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" t="str">
+        <v>**GIRA &amp; PAY2PROFIT обновляют СТАВКИ**
+❗️Специально для своих выбила лучшие условия подключения👇
+**Классика, фермы, залив:**
+0-99к/сутки - 10.5%
+100к-199к/сутки - 11.5%
+от 200к/сутки - 12.5%
+❗️Высокие обороты - индивидуальная ставка
+**БТ:**
+12.5%
+❗️Стабильный оборот от 100к/сутки - повышенная ставка
+**МК:**
+15%
+Страховой депозит прогрессивный - 10% от суточного оборота
+**Минимальный страховой - 150$**
+Пиши сейчас - работай уже через 60 минут
+💌За подключением: @Gira_TL</v>
+      </c>
+      <c r="B131" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" t="str">
+        <v>🚨 **Pro-Level Platform + CRM Built to Crush the Market** 🚨
+⚡️ Flawless 24/7 performance &amp; full automation
+📈 Perfect for Forex, Crypto, CFD &amp; Recovery brands
+💳 Seamless PSP integration – more deposits, less hassle
+🌟 **Your own branded website FREE with every deal**
+🔥 Stop settling for average, level up NOW
+💥 **Everything you need is waiting in my bio**</v>
+      </c>
+      <c r="B132" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132" t="str">
+        <v>ru</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" t="str">
+        <v>☑️ **Подключение к Cube** 🙈
+🔮**C2C / СБП**
+🔴от 1к до 5к ➡️ 15% 
+🔴до 10к ➡️ 13% 
+🦋 **МЕЛКОЧЕК**
+🔴 до 1к ➡️ 17%
+☠️ **КОНТР-АГЕНТЫ** ➡️ 10%
+📝**QR НСПК**
+🔴до 5к ➡️ 16%
+🔴от 5к ➡️ 13%
+✍️огромные объемы трафика✍️
+🛒 **ЯНДЕКС ЧАЕВЫЕ** ➡️ 13%
+✈️ **МОБКОМ**
+🔴до 1к ➡️ 15%
+🔴от 1к ➡️ 15%
+🔴Выход ➡️ 2% 
+📃(Рапира, средн.по стакану) 
+👻БТ out ➡️ 2% 
+🪭OCT out  ➡️ 1%
+🌐 **ТРАНСГРАН** ➡️ 7%
+👑**Локальный трафик****➖**
+🇦🇿 Азербайджан ➡️ 5/1,5%
+🇦🇷 Аргентина ➡️ 4/1%
+🇧🇷 Бразилия ➡️ 0,5/0,5%
+🇪🇬 Египет ➡️ 5/2%
+🇰🇿 Казахстан ➡️ 7/2%
+🇰🇬 Кыргызстан ➡️ 4/1%
+🇲🇩 Молдова ➡️ 5/1,5%
+🇰🇷Южная Корея ➡️ 6/1%
+🇹🇷 Турция ➡️ 5/1,5%
+🇺🇿 Узбекистан ➡️ 1.5/2
+🕷️Страховой депозит: 500$
+🔗Апелляционный депозит: 500$
+💬За подключением в лс - ☑️ **Подключение к Cube** 🙈
+🔮**C2C / СБП**
+🔴от 1к до 5к ➡️ 15% 
+🔴до 10к ➡️ 13% 
+🦋 **МЕЛКОЧЕК**
+🔴 до 1к ➡️ 17%
+☠️ **КОНТР-АГЕНТЫ** ➡️ 10%
+📝**QR НСПК**
+🔴до 5к ➡️ 16%
+🔴от 5к ➡️ 13%
+✍️огромные объемы трафика✍️
+🛒 **ЯНДЕКС ЧАЕВЫЕ** ➡️ 13%
+✈️ **МОБКОМ**
+🔴до 1к ➡️ 15%
+🔴от 1к ➡️ 15%
+🔴Выход ➡️ 2% 
+📃(Рапира, средн.по стакану) 
+👻БТ out ➡️ 2% 
+🪭OCT out  ➡️ 1%
+🌐 **ТРАНСГРАН** ➡️ 7%
+👑**Локальный трафик****➖**
+🇦🇿 Азербайджан ➡️ 5/1,5%
+🇦🇷 Аргентина ➡️ 4/1%
+🇧🇷 Бразилия ➡️ 0,5/0,5%
+🇪🇬 Египет ➡️ 5/2%
+🇰🇿 Казахстан ➡️ 7/2%
+🇰🇬 Кыргызстан ➡️ 4/1%
+🇲🇩 Молдова ➡️ 5/1,5%
+🇰🇷Южная Корея ➡️ 6/1%
+🇹🇷 Турция ➡️ 5/1,5%
+🇺🇿 Узбекистан ➡️ 1.5/2
+🕷️Страховой депозит: 500$
+🔗Апелляционный депозит: 500$
+💬За подключением в лс - rezhunozhem  Butterflly_Knife</v>
+      </c>
+      <c r="B133" t="str">
+        <v>B-1</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133" t="str">
+        <v>ru</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
